--- a/exports/trend_1d/NAUKRI_full_report.xlsx
+++ b/exports/trend_1d/NAUKRI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>7.87</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42026</v>
+        <v>42027</v>
       </c>
       <c r="H2" t="n">
-        <v>156.5</v>
+        <v>155.5</v>
       </c>
       <c r="I2" t="n">
         <v>155.7</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.4</v>
+        <v>-7.99</v>
       </c>
       <c r="L2" t="n">
-        <v>7.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>11.64</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42032</v>
+        <v>42033</v>
       </c>
       <c r="H3" t="n">
-        <v>162.5</v>
+        <v>174</v>
       </c>
       <c r="I3" t="n">
         <v>173.60021327</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.5</v>
+        <v>-11.9</v>
       </c>
       <c r="L3" t="n">
-        <v>5.14</v>
+        <v>14.15</v>
       </c>
       <c r="M3" t="n">
         <v>1.29</v>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>7.08</v>
       </c>
       <c r="O3" t="n">
         <v>-0.64</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.75</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42103</v>
+        <v>42104</v>
       </c>
       <c r="H4" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I4" t="n">
         <v>161.8819723830318</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.9</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>15.8</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.88</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42144</v>
+        <v>42145</v>
       </c>
       <c r="H5" t="n">
-        <v>152.5</v>
+        <v>163.5</v>
       </c>
       <c r="I5" t="n">
         <v>160.8285787926598</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
-        <v>4.69</v>
+        <v>-2.19</v>
       </c>
       <c r="L5" t="n">
         <v>16.25</v>
@@ -726,7 +785,7 @@
         <v>1.88</v>
       </c>
       <c r="N5" t="n">
-        <v>4.69</v>
+        <v>7.21</v>
       </c>
       <c r="O5" t="n">
         <v>-1.23</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>162</v>
+        <v>154.5</v>
       </c>
       <c r="I6" t="n">
         <v>161.1746147511117</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.92</v>
+        <v>-5.5</v>
       </c>
       <c r="L6" t="n">
         <v>7.03</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.35</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42326</v>
+        <v>42327</v>
       </c>
       <c r="H7" t="n">
-        <v>156</v>
+        <v>160.5</v>
       </c>
       <c r="I7" t="n">
         <v>158.0073661757446</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.97</v>
+        <v>-3.88</v>
       </c>
       <c r="L7" t="n">
         <v>11.65</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42398</v>
+        <v>42401</v>
       </c>
       <c r="H8" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I8" t="n">
         <v>158.232211649123</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.93</v>
+        <v>-1.56</v>
       </c>
       <c r="L8" t="n">
         <v>5.92</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>12.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42433</v>
+        <v>42437</v>
       </c>
       <c r="H9" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I9" t="n">
         <v>158.0863658712425</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>2.53</v>
+        <v>-5.06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>6.65</v>
       </c>
       <c r="M9" t="n">
         <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>4.41</v>
+        <v>7.79</v>
       </c>
       <c r="O9" t="n">
         <v>-0.63</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>16.12</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H10" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I10" t="n">
         <v>147.0430025673089</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.24</v>
+        <v>-11.45</v>
       </c>
       <c r="L10" t="n">
-        <v>11.75</v>
+        <v>12.05</v>
       </c>
       <c r="M10" t="n">
         <v>1.56</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.24</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42515</v>
+        <v>42516</v>
       </c>
       <c r="H11" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I11" t="n">
         <v>155.8905144243604</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.76</v>
+        <v>-8.16</v>
       </c>
       <c r="L11" t="n">
         <v>12.59</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.95</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42657</v>
+        <v>42660</v>
       </c>
       <c r="H12" t="n">
-        <v>177</v>
+        <v>172.5</v>
       </c>
       <c r="I12" t="n">
         <v>175.213228190322</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K12" t="n">
-        <v>11.32</v>
+        <v>8.49</v>
       </c>
       <c r="L12" t="n">
         <v>5.66</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42730</v>
+        <v>42731</v>
       </c>
       <c r="H13" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I13" t="n">
         <v>181.7720264122282</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.61</v>
+        <v>-5.51</v>
       </c>
       <c r="L13" t="n">
         <v>18.84</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>14.62</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42824</v>
+        <v>42825</v>
       </c>
       <c r="H14" t="n">
-        <v>162.5</v>
+        <v>160</v>
       </c>
       <c r="I14" t="n">
         <v>160.6652667873096</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.71</v>
+        <v>-12.09</v>
       </c>
       <c r="L14" t="n">
-        <v>11.54</v>
+        <v>12.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.14</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>6.86</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42832</v>
+        <v>42835</v>
       </c>
       <c r="H15" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I15" t="n">
         <v>170.9786320157486</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-5</v>
+        <v>-6.88</v>
       </c>
       <c r="L15" t="n">
         <v>10.31</v>
       </c>
       <c r="M15" t="n">
-        <v>0.31</v>
+        <v>1.19</v>
       </c>
       <c r="N15" t="n">
         <v>2.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42965</v>
+        <v>42968</v>
       </c>
       <c r="H16" t="n">
-        <v>190.5</v>
+        <v>187.5</v>
       </c>
       <c r="I16" t="n">
         <v>187.9670064733839</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K16" t="n">
-        <v>11.4</v>
+        <v>9.65</v>
       </c>
       <c r="L16" t="n">
         <v>6.43</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42990</v>
+        <v>42991</v>
       </c>
       <c r="H17" t="n">
-        <v>199</v>
+        <v>205.5</v>
       </c>
       <c r="I17" t="n">
         <v>202.3985668298997</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.13</v>
+        <v>-9.6</v>
       </c>
       <c r="L17" t="n">
-        <v>9.33</v>
+        <v>12.53</v>
       </c>
       <c r="M17" t="n">
         <v>2.29</v>
       </c>
       <c r="N17" t="n">
-        <v>2.84</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
         <v>-1.57</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H18" t="n">
-        <v>257</v>
+        <v>241.5</v>
       </c>
       <c r="I18" t="n">
         <v>252.8429414898705</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K18" t="n">
-        <v>25.06</v>
+        <v>17.52</v>
       </c>
       <c r="L18" t="n">
         <v>3.89</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>15.29</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43249</v>
+        <v>43250</v>
       </c>
       <c r="H19" t="n">
-        <v>250.5</v>
+        <v>259.5</v>
       </c>
       <c r="I19" t="n">
         <v>254.7127329880282</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.73</v>
+        <v>-7.45</v>
       </c>
       <c r="L19" t="n">
         <v>9.73</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43369</v>
+        <v>43370</v>
       </c>
       <c r="H20" t="n">
-        <v>304.5</v>
+        <v>292</v>
       </c>
       <c r="I20" t="n">
         <v>295.2943167176398</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>17.34</v>
+        <v>12.52</v>
       </c>
       <c r="L20" t="n">
         <v>13.29</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>16.89</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43434</v>
+        <v>43437</v>
       </c>
       <c r="H21" t="n">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="I21" t="n">
         <v>312.9988763598898</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.82</v>
+        <v>-10.27</v>
       </c>
       <c r="L21" t="n">
-        <v>11.3</v>
+        <v>11.99</v>
       </c>
       <c r="M21" t="n">
         <v>3.03</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>12.73</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H22" t="n">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="I22" t="n">
         <v>291.1565008335814</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.9</v>
+        <v>-11.18</v>
       </c>
       <c r="L22" t="n">
-        <v>6.83</v>
+        <v>12.42</v>
       </c>
       <c r="M22" t="n">
-        <v>0.95</v>
+        <v>1.16</v>
       </c>
       <c r="N22" t="n">
-        <v>3.07</v>
+        <v>5.61</v>
       </c>
       <c r="O22" t="n">
         <v>4.21</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.5</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43469</v>
+        <v>43472</v>
       </c>
       <c r="H23" t="n">
-        <v>311.5</v>
+        <v>324.5</v>
       </c>
       <c r="I23" t="n">
         <v>320.0608195228433</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.92</v>
+        <v>-13.46</v>
       </c>
       <c r="L23" t="n">
         <v>17.31</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.02</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43699</v>
+        <v>43700</v>
       </c>
       <c r="H24" t="n">
-        <v>410.5</v>
+        <v>388</v>
       </c>
       <c r="I24" t="n">
         <v>403.2580668511263</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K24" t="n">
-        <v>26.5</v>
+        <v>19.57</v>
       </c>
       <c r="L24" t="n">
         <v>7.09</v>
@@ -1809,7 +2096,7 @@
         <v>2.49</v>
       </c>
       <c r="N24" t="n">
-        <v>5.09</v>
+        <v>5.48</v>
       </c>
       <c r="O24" t="n">
         <v>4.17</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>13.48</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43712</v>
+        <v>43713</v>
       </c>
       <c r="H25" t="n">
-        <v>423.5</v>
+        <v>435</v>
       </c>
       <c r="I25" t="n">
         <v>431.868149597842</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>-9.15</v>
+        <v>-12.11</v>
       </c>
       <c r="L25" t="n">
-        <v>11.6</v>
+        <v>13.92</v>
       </c>
       <c r="M25" t="n">
         <v>1.7</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>12.54</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43719</v>
+        <v>43720</v>
       </c>
       <c r="H26" t="n">
-        <v>392.5</v>
+        <v>372.5</v>
       </c>
       <c r="I26" t="n">
         <v>380.434754613616</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.77</v>
+        <v>-14.37</v>
       </c>
       <c r="L26" t="n">
-        <v>10.34</v>
+        <v>15.4</v>
       </c>
       <c r="M26" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="N26" t="n">
         <v>5.52</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>18.29</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43741</v>
+        <v>43742</v>
       </c>
       <c r="H27" t="n">
-        <v>424.5</v>
+        <v>454</v>
       </c>
       <c r="I27" t="n">
         <v>433.3362017482059</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.96</v>
+        <v>-21.88</v>
       </c>
       <c r="L27" t="n">
-        <v>15.97</v>
+        <v>24.97</v>
       </c>
       <c r="M27" t="n">
         <v>0.9399999999999999</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.64</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H28" t="n">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="I28" t="n">
         <v>545.9191601125154</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K28" t="n">
-        <v>25.11</v>
+        <v>19.38</v>
       </c>
       <c r="L28" t="n">
         <v>5.95</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>15.23</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H29" t="n">
-        <v>401.5</v>
+        <v>471.5</v>
       </c>
       <c r="I29" t="n">
         <v>461.9307237603099</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K29" t="n">
-        <v>25.92</v>
+        <v>13.01</v>
       </c>
       <c r="L29" t="n">
         <v>4.8</v>
@@ -2094,7 +2441,7 @@
         <v>6.04</v>
       </c>
       <c r="N29" t="n">
-        <v>10.94</v>
+        <v>17.43</v>
       </c>
       <c r="O29" t="n">
         <v>-4.58</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>32.64</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H30" t="n">
-        <v>997</v>
+        <v>941.5</v>
       </c>
       <c r="I30" t="n">
         <v>959.4031674339689</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K30" t="n">
-        <v>111.45</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="L30" t="n">
         <v>13.04</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>203</v>
+        <v>204</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>21.23</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44237</v>
+        <v>44238</v>
       </c>
       <c r="H31" t="n">
-        <v>1024</v>
+        <v>1083.5</v>
       </c>
       <c r="I31" t="n">
         <v>1063.251224085104</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.76</v>
+        <v>-15.08</v>
       </c>
       <c r="L31" t="n">
-        <v>9.98</v>
+        <v>16.09</v>
       </c>
       <c r="M31" t="n">
         <v>2.2</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>17.31</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H32" t="n">
-        <v>952.5</v>
+        <v>896</v>
       </c>
       <c r="I32" t="n">
         <v>921.8365048028504</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K32" t="n">
-        <v>-12.09</v>
+        <v>-17.31</v>
       </c>
       <c r="L32" t="n">
-        <v>14.26</v>
+        <v>18.5</v>
       </c>
       <c r="M32" t="n">
         <v>1.88</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>16.31</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
       <c r="H33" t="n">
-        <v>978.5</v>
+        <v>990</v>
       </c>
       <c r="I33" t="n">
         <v>981.3013726463139</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.210000000000001</v>
+        <v>-10.49</v>
       </c>
       <c r="L33" t="n">
-        <v>10.66</v>
+        <v>10.99</v>
       </c>
       <c r="M33" t="n">
         <v>2.71</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>12.52</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44327</v>
+        <v>44328</v>
       </c>
       <c r="H34" t="n">
-        <v>897</v>
+        <v>871</v>
       </c>
       <c r="I34" t="n">
         <v>892.9648275010154</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.390000000000001</v>
+        <v>-12.02</v>
       </c>
       <c r="L34" t="n">
-        <v>9.550000000000001</v>
+        <v>12.32</v>
       </c>
       <c r="M34" t="n">
         <v>1.3</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>12.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44361</v>
+        <v>44362</v>
       </c>
       <c r="H35" t="n">
-        <v>937</v>
+        <v>979.5</v>
       </c>
       <c r="I35" t="n">
         <v>949.4797894482214</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.58</v>
+        <v>-12.46</v>
       </c>
       <c r="L35" t="n">
-        <v>9.01</v>
+        <v>12.74</v>
       </c>
       <c r="M35" t="n">
         <v>1.6</v>
       </c>
       <c r="N35" t="n">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="O35" t="n">
         <v>-2.9</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.19</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H36" t="n">
-        <v>1346</v>
+        <v>1258</v>
       </c>
       <c r="I36" t="n">
         <v>1286.784592477977</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K36" t="n">
-        <v>37.42</v>
+        <v>28.43</v>
       </c>
       <c r="L36" t="n">
         <v>4.03</v>
@@ -2493,7 +2924,7 @@
         <v>1.48</v>
       </c>
       <c r="N36" t="n">
-        <v>4.63</v>
+        <v>6.54</v>
       </c>
       <c r="O36" t="n">
         <v>4.54</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>19.61</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H37" t="n">
-        <v>1000</v>
+        <v>1023</v>
       </c>
       <c r="I37" t="n">
         <v>1013.402748462793</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K37" t="n">
-        <v>20.51</v>
+        <v>18.68</v>
       </c>
       <c r="L37" t="n">
         <v>8.9</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>15.85</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H38" t="n">
-        <v>882.5</v>
+        <v>856</v>
       </c>
       <c r="I38" t="n">
         <v>864.3784385602054</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>-13.73</v>
+        <v>-16.32</v>
       </c>
       <c r="L38" t="n">
-        <v>15.88</v>
+        <v>17.11</v>
       </c>
       <c r="M38" t="n">
         <v>4.3</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>13.93</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H39" t="n">
-        <v>963.5</v>
+        <v>970</v>
       </c>
       <c r="I39" t="n">
         <v>968.2401714755995</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.56</v>
+        <v>-13.32</v>
       </c>
       <c r="L39" t="n">
-        <v>13.32</v>
+        <v>14.08</v>
       </c>
       <c r="M39" t="n">
         <v>2.58</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.09</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H40" t="n">
-        <v>906</v>
+        <v>845</v>
       </c>
       <c r="I40" t="n">
         <v>887.9716239019264</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.6</v>
+        <v>-12.89</v>
       </c>
       <c r="L40" t="n">
-        <v>7.94</v>
+        <v>13.66</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.28</v>
+        <v>6.73</v>
       </c>
       <c r="O40" t="n">
         <v>0.67</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.04</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H41" t="n">
-        <v>761</v>
+        <v>833</v>
       </c>
       <c r="I41" t="n">
         <v>787.2596605299649</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>9.94</v>
+        <v>1.42</v>
       </c>
       <c r="L41" t="n">
         <v>8.279999999999999</v>
@@ -2778,7 +3269,7 @@
         <v>2.72</v>
       </c>
       <c r="N41" t="n">
-        <v>5.19</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O41" t="n">
         <v>-6.73</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>18.96</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H42" t="n">
-        <v>824.5</v>
+        <v>803</v>
       </c>
       <c r="I42" t="n">
         <v>810.6371846565194</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.02</v>
+        <v>-3.6</v>
       </c>
       <c r="L42" t="n">
         <v>15.97</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.22</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H43" t="n">
-        <v>820</v>
+        <v>872</v>
       </c>
       <c r="I43" t="n">
         <v>824.3881486557864</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.12</v>
+        <v>-8.59</v>
       </c>
       <c r="L43" t="n">
-        <v>3.61</v>
+        <v>9.59</v>
       </c>
       <c r="M43" t="n">
         <v>2.49</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>12.19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H44" t="n">
-        <v>819</v>
+        <v>769</v>
       </c>
       <c r="I44" t="n">
         <v>771.0406999565239</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.08</v>
+        <v>-11.81</v>
       </c>
       <c r="L44" t="n">
         <v>12.44</v>
@@ -2949,7 +3476,7 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>5.79</v>
+        <v>6.11</v>
       </c>
       <c r="O44" t="n">
         <v>6.34</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H45" t="n">
-        <v>720.5</v>
+        <v>744.5</v>
       </c>
       <c r="I45" t="n">
         <v>730.062470635703</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K45" t="n">
-        <v>6.31</v>
+        <v>3.19</v>
       </c>
       <c r="L45" t="n">
         <v>5.53</v>
@@ -3006,7 +3545,7 @@
         <v>1.36</v>
       </c>
       <c r="N45" t="n">
-        <v>2.99</v>
+        <v>3.33</v>
       </c>
       <c r="O45" t="n">
         <v>-6.11</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H46" t="n">
-        <v>930</v>
+        <v>892</v>
       </c>
       <c r="I46" t="n">
         <v>899.0665901305747</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K46" t="n">
-        <v>24.92</v>
+        <v>19.81</v>
       </c>
       <c r="L46" t="n">
         <v>3.49</v>
@@ -3063,7 +3614,7 @@
         <v>2.67</v>
       </c>
       <c r="N46" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="O46" t="n">
         <v>3.33</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.88</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H47" t="n">
-        <v>895.5</v>
+        <v>902</v>
       </c>
       <c r="I47" t="n">
         <v>901.5454175789532</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.39</v>
+        <v>-1.12</v>
       </c>
       <c r="L47" t="n">
         <v>5.27</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.09</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H48" t="n">
-        <v>848</v>
+        <v>835.5</v>
       </c>
       <c r="I48" t="n">
         <v>847.1048873457297</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.99</v>
+        <v>-7.37</v>
       </c>
       <c r="L48" t="n">
-        <v>6.43</v>
+        <v>7.82</v>
       </c>
       <c r="M48" t="n">
         <v>1.11</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.9</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H49" t="n">
-        <v>850</v>
+        <v>862.5</v>
       </c>
       <c r="I49" t="n">
         <v>860.792027477578</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.74</v>
+        <v>-3.23</v>
       </c>
       <c r="L49" t="n">
-        <v>3.17</v>
+        <v>4.25</v>
       </c>
       <c r="M49" t="n">
         <v>1.28</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.5</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45320</v>
+        <v>45321</v>
       </c>
       <c r="H50" t="n">
-        <v>995</v>
+        <v>978.5</v>
       </c>
       <c r="I50" t="n">
         <v>978.7591971231545</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K50" t="n">
-        <v>15.36</v>
+        <v>13.45</v>
       </c>
       <c r="L50" t="n">
         <v>1.33</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.39</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45329</v>
+        <v>45330</v>
       </c>
       <c r="H51" t="n">
-        <v>1080</v>
+        <v>1099.5</v>
       </c>
       <c r="I51" t="n">
         <v>1080.183982202095</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.37</v>
+        <v>-12.37</v>
       </c>
       <c r="L51" t="n">
-        <v>10.78</v>
+        <v>12.62</v>
       </c>
       <c r="M51" t="n">
         <v>3.33</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="H52" t="n">
-        <v>1031.5</v>
+        <v>1004.5</v>
       </c>
       <c r="I52" t="n">
         <v>1009.246341654774</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.18</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>8.460000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="M52" t="n">
         <v>0.99</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>10.63</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45378</v>
+        <v>45379</v>
       </c>
       <c r="H53" t="n">
-        <v>1095</v>
+        <v>1118.5</v>
       </c>
       <c r="I53" t="n">
         <v>1104.594223550398</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>-9.01</v>
+        <v>-11.35</v>
       </c>
       <c r="L53" t="n">
-        <v>10.4</v>
+        <v>12.15</v>
       </c>
       <c r="M53" t="n">
         <v>0.64</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.91</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H54" t="n">
-        <v>1184</v>
+        <v>1151</v>
       </c>
       <c r="I54" t="n">
         <v>1151.70937386184</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K54" t="n">
-        <v>5.86</v>
+        <v>2.91</v>
       </c>
       <c r="L54" t="n">
         <v>3.17</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.78</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45462</v>
+        <v>45463</v>
       </c>
       <c r="H55" t="n">
-        <v>1248.5</v>
+        <v>1256.5</v>
       </c>
       <c r="I55" t="n">
         <v>1256.425439332847</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.17</v>
       </c>
       <c r="L55" t="n">
         <v>10.6</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.83</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H56" t="n">
-        <v>1590</v>
+        <v>1530</v>
       </c>
       <c r="I56" t="n">
         <v>1537.651848790683</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K56" t="n">
-        <v>26.54</v>
+        <v>21.77</v>
       </c>
       <c r="L56" t="n">
         <v>1.39</v>
@@ -3633,7 +4304,7 @@
         <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>3.39</v>
+        <v>3.77</v>
       </c>
       <c r="O56" t="n">
         <v>0.64</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>10.77</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="H57" t="n">
-        <v>1600</v>
+        <v>1639</v>
       </c>
       <c r="I57" t="n">
         <v>1633.363944816058</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.58</v>
+        <v>-7.12</v>
       </c>
       <c r="L57" t="n">
-        <v>5.88</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M57" t="n">
         <v>2.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.06</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H58" t="n">
-        <v>1687.5</v>
+        <v>1647.5</v>
       </c>
       <c r="I58" t="n">
         <v>1662.902666026119</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K58" t="n">
-        <v>2.96</v>
+        <v>0.52</v>
       </c>
       <c r="L58" t="n">
         <v>2.2</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>10.53</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="H59" t="n">
-        <v>1588</v>
+        <v>1610</v>
       </c>
       <c r="I59" t="n">
         <v>1599.837080634404</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K59" t="n">
-        <v>3.61</v>
+        <v>2.28</v>
       </c>
       <c r="L59" t="n">
         <v>2.82</v>
       </c>
       <c r="M59" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="N59" t="n">
         <v>4.16</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="H60" t="n">
-        <v>1507.5</v>
+        <v>1430.5</v>
       </c>
       <c r="I60" t="n">
         <v>1455.322424584763</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.37</v>
+        <v>-11.15</v>
       </c>
       <c r="L60" t="n">
-        <v>10.22</v>
+        <v>11.37</v>
       </c>
       <c r="M60" t="n">
         <v>1.14</v>
       </c>
       <c r="N60" t="n">
-        <v>3.24</v>
+        <v>5.11</v>
       </c>
       <c r="O60" t="n">
         <v>1.39</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>13.32</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H61" t="n">
-        <v>1390.5</v>
+        <v>1417</v>
       </c>
       <c r="I61" t="n">
         <v>1413.675415339469</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K61" t="n">
-        <v>2.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L61" t="n">
         <v>4.37</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.94</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H62" t="n">
-        <v>1420.1</v>
+        <v>1375.2</v>
       </c>
       <c r="I62" t="n">
         <v>1399.732383875939</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K62" t="n">
-        <v>0.22</v>
+        <v>-2.95</v>
       </c>
       <c r="L62" t="n">
         <v>6.92</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.87</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H63" t="n">
-        <v>1028.05</v>
+        <v>1047.7</v>
       </c>
       <c r="I63" t="n">
         <v>1039.610730366234</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K63" t="n">
-        <v>25.24</v>
+        <v>23.81</v>
       </c>
       <c r="L63" t="n">
         <v>7.98</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>10</v>
+      </c>
+      <c r="U63" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>10.43</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H64" t="n">
-        <v>991.65</v>
+        <v>972.85</v>
       </c>
       <c r="I64" t="n">
         <v>978.4086926549354</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.35</v>
+        <v>-7.14</v>
       </c>
       <c r="L64" t="n">
-        <v>6.52</v>
+        <v>7.58</v>
       </c>
       <c r="M64" t="n">
         <v>1.09</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.83</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H65" t="n">
-        <v>1004.05</v>
+        <v>1015.7</v>
       </c>
       <c r="I65" t="n">
         <v>1006.774728224707</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.21</v>
+        <v>-4.4</v>
       </c>
       <c r="L65" t="n">
         <v>7.7</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>12.74</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H66" t="n">
-        <v>1265</v>
+        <v>1250.8</v>
       </c>
       <c r="I66" t="n">
         <v>1255.902224955818</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K66" t="n">
-        <v>24.54</v>
+        <v>23.15</v>
       </c>
       <c r="L66" t="n">
         <v>6.56</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>31</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9221,7 +10032,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.9</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="6">
@@ -9231,7 +10042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -9241,7 +10052,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
@@ -9251,7 +10062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9261,7 +10072,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -9271,7 +10082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131.2</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -9281,7 +10092,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -9291,7 +10102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -9301,7 +10112,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.9</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="14">
@@ -9311,7 +10122,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.05</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="15">
@@ -9321,7 +10132,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.29</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="16">
@@ -9331,7 +10142,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.31</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="17">
@@ -9341,7 +10152,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111.45</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -9351,7 +10162,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36.9</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="19">
@@ -9361,7 +10172,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.68</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9371,7 +10182,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.279999999999999</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="21">
@@ -9381,7 +10192,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.84</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="22">
@@ -9391,7 +10202,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -9401,7 +10212,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -9411,7 +10222,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="25">
@@ -9431,7 +10242,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.01</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="27">
@@ -9441,7 +10252,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.24</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="28">
@@ -9451,7 +10262,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
